--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(CCI).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(CCI).xlsx
@@ -562,7 +562,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -742,6 +742,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -751,7 +754,7 @@
               <c:f>'model2(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -930,6 +933,9 @@
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>1158493.0294822238</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
               </c:numCache>
@@ -973,7 +979,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1153,6 +1159,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1162,7 +1171,7 @@
               <c:f>'model2(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1342,6 +1351,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1978849.1612350328</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2022104.2217609019</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1384,7 +1396,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1564,6 +1576,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1573,7 +1588,7 @@
               <c:f>'model2(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1753,6 +1768,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>820356.13175280904</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>863611.19227867806</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1774,11 +1792,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="99720576"/>
-        <c:axId val="103724544"/>
+        <c:axId val="494485888"/>
+        <c:axId val="494488192"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="99720576"/>
+        <c:axId val="494485888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1821,14 +1839,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="103724544"/>
+        <c:crossAx val="494488192"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="103724544"/>
+        <c:axId val="494488192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1879,7 +1897,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99720576"/>
+        <c:crossAx val="494485888"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2040,7 +2058,7 @@
               <c:f>'model2(2)vol&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2220,6 +2238,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-273879.41101316386</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-703792.54386857653</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2234,8 +2255,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="453155840"/>
-        <c:axId val="453154304"/>
+        <c:axId val="517973504"/>
+        <c:axId val="517971968"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2260,7 +2281,7 @@
               <c:f>'model2(2)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2440,6 +2461,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2449,7 +2473,7 @@
               <c:f>'model2(2)vol&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2629,6 +2653,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2645,11 +2672,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="453150976"/>
-        <c:axId val="453152768"/>
+        <c:axId val="517935872"/>
+        <c:axId val="517937408"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="453150976"/>
+        <c:axId val="517935872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2692,14 +2719,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="453152768"/>
+        <c:crossAx val="517937408"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="453152768"/>
+        <c:axId val="517937408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2750,12 +2777,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="453150976"/>
+        <c:crossAx val="517935872"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="453154304"/>
+        <c:axId val="517971968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2792,12 +2819,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="453155840"/>
+        <c:crossAx val="517973504"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="453155840"/>
+        <c:axId val="517973504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2806,7 +2833,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="453154304"/>
+        <c:crossAx val="517971968"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2938,7 +2965,7 @@
               <c:f>'model2(1)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3118,6 +3145,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-36057.366675283578</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-60139.263576626639</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3132,8 +3162,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="424745216"/>
-        <c:axId val="399842688"/>
+        <c:axId val="566694272"/>
+        <c:axId val="566655616"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -3158,7 +3188,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3338,6 +3368,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3347,7 +3380,7 @@
               <c:f>'model2(1)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -3527,6 +3560,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3543,11 +3579,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="399839232"/>
-        <c:axId val="399840768"/>
+        <c:axId val="566651904"/>
+        <c:axId val="566653696"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="399839232"/>
+        <c:axId val="566651904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3590,14 +3626,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="399840768"/>
+        <c:crossAx val="566653696"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="399840768"/>
+        <c:axId val="566653696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3648,12 +3684,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="399839232"/>
+        <c:crossAx val="566651904"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="399842688"/>
+        <c:axId val="566655616"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3690,12 +3726,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="424745216"/>
+        <c:crossAx val="566694272"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="424745216"/>
+        <c:axId val="566694272"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3704,7 +3740,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="399842688"/>
+        <c:crossAx val="566655616"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3854,7 +3890,7 @@
               <c:f>'model2(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4034,6 +4070,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4043,7 +4082,7 @@
               <c:f>'model2(1)&amp;CCI_per_month'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4222,6 +4261,9 @@
                   <c:v>1222236.9259249454</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>1222236.9259249454</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>1222236.9259249454</c:v>
                 </c:pt>
               </c:numCache>
@@ -4265,7 +4307,7 @@
               <c:f>'model2(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4445,6 +4487,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4454,7 +4499,7 @@
               <c:f>'model2(1)&amp;CCI_per_month'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4634,6 +4679,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>2097331.2663571048</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2142805.2789050131</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4676,7 +4724,7 @@
               <c:f>'model2(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4856,6 +4904,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4865,7 +4916,7 @@
               <c:f>'model2(1)&amp;CCI_per_month'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5045,6 +5096,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>875094.34043215937</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>920568.35298006772</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5066,11 +5120,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="448737280"/>
-        <c:axId val="448739200"/>
+        <c:axId val="569538048"/>
+        <c:axId val="569539584"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="448737280"/>
+        <c:axId val="569538048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5113,14 +5167,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="448739200"/>
+        <c:crossAx val="569539584"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="448739200"/>
+        <c:axId val="569539584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5171,7 +5225,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="448737280"/>
+        <c:crossAx val="569538048"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5332,7 +5386,7 @@
               <c:f>'model2(1)&amp;CCI_per_month'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5512,6 +5566,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-43268.840010340289</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-72167.11629195197</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5526,8 +5583,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="471177472"/>
-        <c:axId val="471175552"/>
+        <c:axId val="502057216"/>
+        <c:axId val="502055680"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -5552,7 +5609,7 @@
               <c:f>'model2(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5732,6 +5789,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5741,7 +5801,7 @@
               <c:f>'model2(1)&amp;CCI_per_month'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -5921,6 +5981,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5937,11 +6000,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="458265344"/>
-        <c:axId val="458267264"/>
+        <c:axId val="502048256"/>
+        <c:axId val="502049792"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="458265344"/>
+        <c:axId val="502048256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5984,14 +6047,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="458267264"/>
+        <c:crossAx val="502049792"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="458267264"/>
+        <c:axId val="502049792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6042,12 +6105,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="458265344"/>
+        <c:crossAx val="502048256"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="471175552"/>
+        <c:axId val="502055680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6084,12 +6147,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="471177472"/>
+        <c:crossAx val="502057216"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="471177472"/>
+        <c:axId val="502057216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6098,7 +6161,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="471175552"/>
+        <c:crossAx val="502055680"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6248,7 +6311,7 @@
               <c:f>'model2(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6428,6 +6491,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6437,7 +6503,7 @@
               <c:f>'model2(1)&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6616,6 +6682,9 @@
                   <c:v>1226222.9374500697</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>1226222.9374500697</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>1226222.9374500697</c:v>
                 </c:pt>
               </c:numCache>
@@ -6659,7 +6728,7 @@
               <c:f>'model2(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6839,6 +6908,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6848,7 +6920,7 @@
               <c:f>'model2(1)&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7028,6 +7100,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>2098477.6097613247</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2144300.0487286719</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7070,7 +7145,7 @@
               <c:f>'model2(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7250,6 +7325,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7259,7 +7337,7 @@
               <c:f>'model2(1)&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7439,6 +7517,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>872254.67231125501</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>918077.11127860215</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7460,11 +7541,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="524067968"/>
-        <c:axId val="524069504"/>
+        <c:axId val="502158848"/>
+        <c:axId val="502160384"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="524067968"/>
+        <c:axId val="502158848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7507,14 +7588,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="524069504"/>
+        <c:crossAx val="502160384"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="524069504"/>
+        <c:axId val="502160384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7565,7 +7646,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="524067968"/>
+        <c:crossAx val="502158848"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7726,7 +7807,7 @@
               <c:f>'model2(1)&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7906,6 +7987,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-43268.840010340289</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-60139.263576626639</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7920,8 +8004,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="442327424"/>
-        <c:axId val="614939264"/>
+        <c:axId val="502192000"/>
+        <c:axId val="502190464"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7946,7 +8030,7 @@
               <c:f>'model2(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8126,6 +8210,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8135,7 +8222,7 @@
               <c:f>'model2(1)&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8315,6 +8402,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8331,11 +8421,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="610503680"/>
-        <c:axId val="614937344"/>
+        <c:axId val="502174848"/>
+        <c:axId val="502176384"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="610503680"/>
+        <c:axId val="502174848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8378,14 +8468,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="614937344"/>
+        <c:crossAx val="502176384"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="614937344"/>
+        <c:axId val="502176384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8436,12 +8526,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="610503680"/>
+        <c:crossAx val="502174848"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="614939264"/>
+        <c:axId val="502190464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8478,12 +8568,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="442327424"/>
+        <c:crossAx val="502192000"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="442327424"/>
+        <c:axId val="502192000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8492,7 +8582,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="614939264"/>
+        <c:crossAx val="502190464"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8642,7 +8732,7 @@
               <c:f>'model2(2)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8822,6 +8912,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8831,7 +8924,7 @@
               <c:f>'model2(2)&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9010,6 +9103,9 @@
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>9962785.3792499099</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
               </c:numCache>
@@ -9053,7 +9149,7 @@
               <c:f>'model2(2)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9233,6 +9329,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9242,7 +9341,7 @@
               <c:f>'model2(2)&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9422,6 +9521,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>17567754.333578344</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>17963358.223627001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9464,7 +9566,7 @@
               <c:f>'model2(2)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9644,6 +9746,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9653,7 +9758,7 @@
               <c:f>'model2(2)&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9833,6 +9938,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>7604968.9543284345</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>8000572.8443770912</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9854,11 +9962,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="442363264"/>
-        <c:axId val="442365056"/>
+        <c:axId val="502277248"/>
+        <c:axId val="502278784"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="442363264"/>
+        <c:axId val="502277248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9901,14 +10009,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="442365056"/>
+        <c:crossAx val="502278784"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="442365056"/>
+        <c:axId val="502278784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9959,7 +10067,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="442363264"/>
+        <c:crossAx val="502277248"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10120,7 +10228,7 @@
               <c:f>'model2(2)&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10300,6 +10408,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>12761408.348849542</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>12043831.475181028</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10314,8 +10425,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="452603264"/>
-        <c:axId val="452601728"/>
+        <c:axId val="502298112"/>
+        <c:axId val="502296576"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10340,7 +10451,7 @@
               <c:f>'model2(2)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10520,6 +10631,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10529,7 +10643,7 @@
               <c:f>'model2(2)&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10709,6 +10823,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10725,11 +10842,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="452594304"/>
-        <c:axId val="452600192"/>
+        <c:axId val="502293248"/>
+        <c:axId val="502294784"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="452594304"/>
+        <c:axId val="502293248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10772,14 +10889,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="452600192"/>
+        <c:crossAx val="502294784"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="452600192"/>
+        <c:axId val="502294784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10830,12 +10947,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="452594304"/>
+        <c:crossAx val="502293248"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="452601728"/>
+        <c:axId val="502296576"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10872,12 +10989,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="452603264"/>
+        <c:crossAx val="502298112"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="452603264"/>
+        <c:axId val="502298112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10886,7 +11003,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="452601728"/>
+        <c:crossAx val="502296576"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11036,7 +11153,7 @@
               <c:f>'model2(2)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11216,6 +11333,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11225,7 +11345,7 @@
               <c:f>'model2(2)vol&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11404,6 +11524,9 @@
                   <c:v>8864712.2860347666</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>8864712.2860347666</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>8864712.2860347666</c:v>
                 </c:pt>
               </c:numCache>
@@ -11447,7 +11570,7 @@
               <c:f>'model2(2)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11627,6 +11750,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11636,7 +11762,7 @@
               <c:f>'model2(2)vol&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11816,6 +11942,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>16990140.268494405</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>17388332.741541885</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11858,7 +11987,7 @@
               <c:f>'model2(2)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12038,6 +12167,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12047,7 +12179,7 @@
               <c:f>'model2(2)vol&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12227,6 +12359,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>8125427.9824596383</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>8523620.4555071183</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12248,11 +12383,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="453118592"/>
-        <c:axId val="453128576"/>
+        <c:axId val="517362432"/>
+        <c:axId val="517363968"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="453118592"/>
+        <c:axId val="517362432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12295,14 +12430,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="453128576"/>
+        <c:crossAx val="517363968"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="453128576"/>
+        <c:axId val="517363968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12353,7 +12488,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="453118592"/>
+        <c:crossAx val="517362432"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13067,7 +13202,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG62"/>
+  <dimension ref="A1:AG63"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -15710,6 +15845,44 @@
         <v>241671.12627942342</v>
       </c>
     </row>
+    <row r="63" spans="1:12" ht="12.75">
+      <c r="A63" s="12">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="13">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="13">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="14">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="14">
+        <v>-60139.263576626639</v>
+      </c>
+      <c r="F63" s="15">
+        <v>-47131.083462289775</v>
+      </c>
+      <c r="G63" s="15">
+        <v>1348192.6340495073</v>
+      </c>
+      <c r="H63" s="15">
+        <v>1720293.8319048518</v>
+      </c>
+      <c r="I63" s="15">
+        <v>1158493.0294822238</v>
+      </c>
+      <c r="J63" s="15">
+        <v>2022104.2217609019</v>
+      </c>
+      <c r="K63" s="15">
+        <v>863611.19227867806</v>
+      </c>
+      <c r="L63" s="14">
+        <v>301810.38985605008</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -15726,7 +15899,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AM62"/>
+  <dimension ref="A1:AM63"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -19823,6 +19996,71 @@
         <v>1.2</v>
       </c>
     </row>
+    <row r="63" spans="1:21" ht="12.75">
+      <c r="A63" s="12">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="13">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="13">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="14">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="14">
+        <v>-72167.11629195197</v>
+      </c>
+      <c r="F63" s="15">
+        <v>-56557.300154747725</v>
+      </c>
+      <c r="G63" s="15">
+        <v>1410345.4730035041</v>
+      </c>
+      <c r="H63" s="15">
+        <v>1799600.8558327174</v>
+      </c>
+      <c r="I63" s="15">
+        <v>1222236.9259249454</v>
+      </c>
+      <c r="J63" s="15">
+        <v>2142805.2789050131</v>
+      </c>
+      <c r="K63" s="15">
+        <v>920568.35298006772</v>
+      </c>
+      <c r="L63" s="14">
+        <v>343204.42307229573</v>
+      </c>
+      <c r="M63" s="23">
+        <v>1.2970000505447388</v>
+      </c>
+      <c r="N63" s="23">
+        <v>1.1710000038146973</v>
+      </c>
+      <c r="O63" s="23">
+        <v>1.2480000257492065</v>
+      </c>
+      <c r="P63" s="23">
+        <v>1.0304285770370849</v>
+      </c>
+      <c r="Q63" s="23">
+        <v>0.21757144871212164</v>
+      </c>
+      <c r="R63" s="23">
+        <v>0.10519728409189744</v>
+      </c>
+      <c r="S63" s="9">
+        <v>1.5779592613784615E-3</v>
+      </c>
+      <c r="T63" s="9">
+        <v>137.88153727242442</v>
+      </c>
+      <c r="U63" s="11">
+        <v>1.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -19839,7 +20077,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AG62"/>
+  <dimension ref="A1:AG63"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -22831,6 +23069,50 @@
         <v>1.2</v>
       </c>
     </row>
+    <row r="63" spans="1:14" ht="12.75">
+      <c r="A63" s="12">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="13">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="13">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="14">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="14">
+        <v>-60139.263576626639</v>
+      </c>
+      <c r="F63" s="15">
+        <v>-47131.083462289775</v>
+      </c>
+      <c r="G63" s="15">
+        <v>1431011.2450437082</v>
+      </c>
+      <c r="H63" s="15">
+        <v>1825970.3814290198</v>
+      </c>
+      <c r="I63" s="15">
+        <v>1226222.9374500697</v>
+      </c>
+      <c r="J63" s="15">
+        <v>2144300.0487286719</v>
+      </c>
+      <c r="K63" s="15">
+        <v>918077.11127860215</v>
+      </c>
+      <c r="L63" s="14">
+        <v>318329.66729965212</v>
+      </c>
+      <c r="M63" s="9">
+        <v>66.335527216233743</v>
+      </c>
+      <c r="N63" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -22847,7 +23129,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG62"/>
+  <dimension ref="A1:AG63"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -25839,6 +26121,50 @@
         <v>1.2</v>
       </c>
     </row>
+    <row r="63" spans="1:14" ht="12.75">
+      <c r="A63" s="12">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="13">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="13">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="14">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="14">
+        <v>-915628.10722505616</v>
+      </c>
+      <c r="F63" s="15">
+        <v>-717576.87366851489</v>
+      </c>
+      <c r="G63" s="15">
+        <v>12043831.475181028</v>
+      </c>
+      <c r="H63" s="15">
+        <v>15367929.237992419</v>
+      </c>
+      <c r="I63" s="15">
+        <v>9962785.3792499099</v>
+      </c>
+      <c r="J63" s="15">
+        <v>17963358.223627001</v>
+      </c>
+      <c r="K63" s="15">
+        <v>8000572.8443770912</v>
+      </c>
+      <c r="L63" s="14">
+        <v>2595428.9856345826</v>
+      </c>
+      <c r="M63" s="9">
+        <v>66.335527216233743</v>
+      </c>
+      <c r="N63" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -25855,7 +26181,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AI62"/>
+  <dimension ref="A1:AI63"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -29215,6 +29541,56 @@
         <v>1.2</v>
       </c>
     </row>
+    <row r="63" spans="1:16" ht="12.75">
+      <c r="A63" s="12">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="13">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="13">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="14">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="14">
+        <v>3094800</v>
+      </c>
+      <c r="F63" s="14">
+        <v>4026308.4497372219</v>
+      </c>
+      <c r="G63" s="14">
+        <v>-703792.54386857653</v>
+      </c>
+      <c r="H63" s="15">
+        <v>-551561.54486233124</v>
+      </c>
+      <c r="I63" s="15">
+        <v>12293349.432560524</v>
+      </c>
+      <c r="J63" s="15">
+        <v>15686314.157319667</v>
+      </c>
+      <c r="K63" s="15">
+        <v>8864712.2860347666</v>
+      </c>
+      <c r="L63" s="15">
+        <v>17388332.741541885</v>
+      </c>
+      <c r="M63" s="15">
+        <v>8523620.4555071183</v>
+      </c>
+      <c r="N63" s="14">
+        <v>1702018.5842222178</v>
+      </c>
+      <c r="O63" s="9">
+        <v>66.335527216233743</v>
+      </c>
+      <c r="P63" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="J2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(CCI).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(CCI).xlsx
@@ -562,7 +562,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -745,6 +745,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -754,7 +757,7 @@
               <c:f>'model2(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -936,6 +939,9 @@
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
                 <c:pt idx="60">
+                  <c:v>1158493.0294822238</c:v>
+                </c:pt>
+                <c:pt idx="61">
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
               </c:numCache>
@@ -979,7 +985,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1162,6 +1168,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1171,7 +1180,7 @@
               <c:f>'model2(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1354,6 +1363,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>2022104.2217609019</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1794259.6267486978</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1396,7 +1408,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1579,6 +1591,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1588,7 +1603,7 @@
               <c:f>'model2(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1771,6 +1786,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>863611.19227867806</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>635766.59726647404</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1792,11 +1810,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="494485888"/>
-        <c:axId val="494488192"/>
+        <c:axId val="541882624"/>
+        <c:axId val="542040064"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="494485888"/>
+        <c:axId val="541882624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1839,14 +1857,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="494488192"/>
+        <c:crossAx val="542040064"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="494488192"/>
+        <c:axId val="542040064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1897,7 +1915,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="494485888"/>
+        <c:crossAx val="541882624"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2058,7 +2076,7 @@
               <c:f>'model2(2)vol&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2241,6 +2259,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>-703792.54386857653</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-351576.30531150417</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2255,8 +2276,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="517973504"/>
-        <c:axId val="517971968"/>
+        <c:axId val="567400704"/>
+        <c:axId val="567399168"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2281,7 +2302,7 @@
               <c:f>'model2(2)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2464,6 +2485,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2473,7 +2497,7 @@
               <c:f>'model2(2)vol&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2656,6 +2680,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>1.2760000228881836</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1.1069999933242798</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2672,11 +2699,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="517935872"/>
-        <c:axId val="517937408"/>
+        <c:axId val="567395840"/>
+        <c:axId val="567397376"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="517935872"/>
+        <c:axId val="567395840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2719,14 +2746,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="517937408"/>
+        <c:crossAx val="567397376"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="517937408"/>
+        <c:axId val="567397376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2777,12 +2804,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="517935872"/>
+        <c:crossAx val="567395840"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="517971968"/>
+        <c:axId val="567399168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2819,12 +2846,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="517973504"/>
+        <c:crossAx val="567400704"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="517973504"/>
+        <c:axId val="567400704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2833,7 +2860,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="517971968"/>
+        <c:crossAx val="567399168"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2965,7 +2992,7 @@
               <c:f>'model2(1)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3148,6 +3175,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>-60139.263576626639</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-35250.090060671617</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3162,8 +3192,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="566694272"/>
-        <c:axId val="566655616"/>
+        <c:axId val="676456320"/>
+        <c:axId val="676454400"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -3188,7 +3218,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3371,6 +3401,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3380,7 +3413,7 @@
               <c:f>'model2(1)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -3563,6 +3596,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>1.2760000228881836</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1.1069999933242798</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3579,11 +3615,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="566651904"/>
-        <c:axId val="566653696"/>
+        <c:axId val="572617088"/>
+        <c:axId val="572619008"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="566651904"/>
+        <c:axId val="572617088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3626,14 +3662,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566653696"/>
+        <c:crossAx val="572619008"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="566653696"/>
+        <c:axId val="572619008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3684,12 +3720,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566651904"/>
+        <c:crossAx val="572617088"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="566655616"/>
+        <c:axId val="676454400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3726,12 +3762,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566694272"/>
+        <c:crossAx val="676456320"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="566694272"/>
+        <c:axId val="676456320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3740,7 +3776,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="566655616"/>
+        <c:crossAx val="676454400"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3890,7 +3926,7 @@
               <c:f>'model2(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4073,6 +4109,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4082,7 +4121,7 @@
               <c:f>'model2(1)&amp;CCI_per_month'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4264,6 +4303,9 @@
                   <c:v>1222236.9259249454</c:v>
                 </c:pt>
                 <c:pt idx="60">
+                  <c:v>1222236.9259249454</c:v>
+                </c:pt>
+                <c:pt idx="61">
                   <c:v>1222236.9259249454</c:v>
                 </c:pt>
               </c:numCache>
@@ -4307,7 +4349,7 @@
               <c:f>'model2(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4490,6 +4532,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4499,7 +4544,7 @@
               <c:f>'model2(1)&amp;CCI_per_month'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4682,6 +4727,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>2142805.2789050131</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1904456.8522721031</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4724,7 +4772,7 @@
               <c:f>'model2(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4907,6 +4955,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4916,7 +4967,7 @@
               <c:f>'model2(1)&amp;CCI_per_month'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5099,6 +5150,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>920568.35298006772</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>682219.92634715769</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5120,11 +5174,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="569538048"/>
-        <c:axId val="569539584"/>
+        <c:axId val="677705600"/>
+        <c:axId val="677724160"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="569538048"/>
+        <c:axId val="677705600"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5167,14 +5221,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="569539584"/>
+        <c:crossAx val="677724160"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="569539584"/>
+        <c:axId val="677724160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5225,7 +5279,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="569538048"/>
+        <c:crossAx val="677705600"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5386,7 +5440,7 @@
               <c:f>'model2(1)&amp;CCI_per_month'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5569,6 +5623,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>-72167.11629195197</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-35250.090060671617</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5583,8 +5640,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="502057216"/>
-        <c:axId val="502055680"/>
+        <c:axId val="412220800"/>
+        <c:axId val="412219264"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -5609,7 +5666,7 @@
               <c:f>'model2(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5792,6 +5849,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5801,7 +5861,7 @@
               <c:f>'model2(1)&amp;CCI_per_month'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -5984,6 +6044,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>1.2760000228881836</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1.1069999933242798</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6000,11 +6063,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="502048256"/>
-        <c:axId val="502049792"/>
+        <c:axId val="412211840"/>
+        <c:axId val="412217728"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="502048256"/>
+        <c:axId val="412211840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6047,14 +6110,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="502049792"/>
+        <c:crossAx val="412217728"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="502049792"/>
+        <c:axId val="412217728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6105,12 +6168,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="502048256"/>
+        <c:crossAx val="412211840"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="502055680"/>
+        <c:axId val="412219264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6147,12 +6210,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="502057216"/>
+        <c:crossAx val="412220800"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="502057216"/>
+        <c:axId val="412220800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6161,7 +6224,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="502055680"/>
+        <c:crossAx val="412219264"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6311,7 +6374,7 @@
               <c:f>'model2(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6494,6 +6557,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6503,7 +6569,7 @@
               <c:f>'model2(1)&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6685,6 +6751,9 @@
                   <c:v>1226222.9374500697</c:v>
                 </c:pt>
                 <c:pt idx="60">
+                  <c:v>1226222.9374500697</c:v>
+                </c:pt>
+                <c:pt idx="61">
                   <c:v>1226222.9374500697</c:v>
                 </c:pt>
               </c:numCache>
@@ -6728,7 +6797,7 @@
               <c:f>'model2(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6911,6 +6980,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6920,7 +6992,7 @@
               <c:f>'model2(1)&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7103,6 +7175,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>2144300.0487286719</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1902459.1060100065</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7145,7 +7220,7 @@
               <c:f>'model2(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7328,6 +7403,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7337,7 +7415,7 @@
               <c:f>'model2(1)&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7520,6 +7598,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>918077.11127860215</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>676236.16855993681</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7541,11 +7622,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="502158848"/>
-        <c:axId val="502160384"/>
+        <c:axId val="566295168"/>
+        <c:axId val="566296960"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="502158848"/>
+        <c:axId val="566295168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7588,14 +7669,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="502160384"/>
+        <c:crossAx val="566296960"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="502160384"/>
+        <c:axId val="566296960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7646,7 +7727,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="502158848"/>
+        <c:crossAx val="566295168"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7807,7 +7888,7 @@
               <c:f>'model2(1)&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7990,6 +8071,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>-60139.263576626639</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-35250.090060671617</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8004,8 +8088,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="502192000"/>
-        <c:axId val="502190464"/>
+        <c:axId val="566340992"/>
+        <c:axId val="566339456"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -8030,7 +8114,7 @@
               <c:f>'model2(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8213,6 +8297,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8222,7 +8309,7 @@
               <c:f>'model2(1)&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8405,6 +8492,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>1.2760000228881836</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1.1069999933242798</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8421,11 +8511,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="502174848"/>
-        <c:axId val="502176384"/>
+        <c:axId val="566319744"/>
+        <c:axId val="566337920"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="502174848"/>
+        <c:axId val="566319744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8468,14 +8558,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="502176384"/>
+        <c:crossAx val="566337920"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="502176384"/>
+        <c:axId val="566337920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8526,12 +8616,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="502174848"/>
+        <c:crossAx val="566319744"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="502190464"/>
+        <c:axId val="566339456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8568,12 +8658,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="502192000"/>
+        <c:crossAx val="566340992"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="502192000"/>
+        <c:axId val="566340992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8582,7 +8672,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="502190464"/>
+        <c:crossAx val="566339456"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8732,7 +8822,7 @@
               <c:f>'model2(2)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8915,6 +9005,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8924,7 +9017,7 @@
               <c:f>'model2(2)&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9106,6 +9199,9 @@
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
                 <c:pt idx="60">
+                  <c:v>9962785.3792499099</c:v>
+                </c:pt>
+                <c:pt idx="61">
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
               </c:numCache>
@@ -9149,7 +9245,7 @@
               <c:f>'model2(2)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9332,6 +9428,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9341,7 +9440,7 @@
               <c:f>'model2(2)&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9524,6 +9623,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>17963358.223627001</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>15927950.34825873</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9566,7 +9668,7 @@
               <c:f>'model2(2)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9749,6 +9851,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9758,7 +9863,7 @@
               <c:f>'model2(2)&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9941,6 +10046,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>8000572.8443770912</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>5965164.9690088201</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9962,11 +10070,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="502277248"/>
-        <c:axId val="502278784"/>
+        <c:axId val="566381184"/>
+        <c:axId val="566399360"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="502277248"/>
+        <c:axId val="566381184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10009,14 +10117,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="502278784"/>
+        <c:crossAx val="566399360"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="502278784"/>
+        <c:axId val="566399360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10067,7 +10175,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="502277248"/>
+        <c:crossAx val="566381184"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10228,7 +10336,7 @@
               <c:f>'model2(2)&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10411,6 +10519,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>12043831.475181028</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>11759663.097474437</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10425,8 +10536,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="502298112"/>
-        <c:axId val="502296576"/>
+        <c:axId val="566430720"/>
+        <c:axId val="566429184"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10451,7 +10562,7 @@
               <c:f>'model2(2)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10634,6 +10745,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10643,7 +10757,7 @@
               <c:f>'model2(2)&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10826,6 +10940,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>1.2760000228881836</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1.1069999933242798</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10842,11 +10959,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="502293248"/>
-        <c:axId val="502294784"/>
+        <c:axId val="566417664"/>
+        <c:axId val="566427648"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="502293248"/>
+        <c:axId val="566417664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10889,14 +11006,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="502294784"/>
+        <c:crossAx val="566427648"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="502294784"/>
+        <c:axId val="566427648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10947,12 +11064,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="502293248"/>
+        <c:crossAx val="566417664"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="502296576"/>
+        <c:axId val="566429184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10989,12 +11106,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="502298112"/>
+        <c:crossAx val="566430720"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="502298112"/>
+        <c:axId val="566430720"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11003,7 +11120,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="502296576"/>
+        <c:crossAx val="566429184"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11153,7 +11270,7 @@
               <c:f>'model2(2)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11336,6 +11453,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11345,7 +11465,7 @@
               <c:f>'model2(2)vol&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11527,6 +11647,9 @@
                   <c:v>8864712.2860347666</c:v>
                 </c:pt>
                 <c:pt idx="60">
+                  <c:v>8864712.2860347666</c:v>
+                </c:pt>
+                <c:pt idx="61">
                   <c:v>8864712.2860347666</c:v>
                 </c:pt>
               </c:numCache>
@@ -11570,7 +11693,7 @@
               <c:f>'model2(2)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11753,6 +11876,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11762,7 +11888,7 @@
               <c:f>'model2(2)vol&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11945,6 +12071,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>17388332.741541885</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>15310756.323999755</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11987,7 +12116,7 @@
               <c:f>'model2(2)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12170,6 +12299,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12179,7 +12311,7 @@
               <c:f>'model2(2)vol&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12362,6 +12494,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>8523620.4555071183</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>6446044.0379649885</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12383,11 +12518,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="517362432"/>
-        <c:axId val="517363968"/>
+        <c:axId val="567372032"/>
+        <c:axId val="567373824"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="517362432"/>
+        <c:axId val="567372032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12430,14 +12565,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="517363968"/>
+        <c:crossAx val="567373824"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="517363968"/>
+        <c:axId val="567373824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12488,7 +12623,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="517362432"/>
+        <c:crossAx val="567372032"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13202,7 +13337,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG63"/>
+  <dimension ref="A1:AG64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -15883,6 +16018,44 @@
         <v>301810.38985605008</v>
       </c>
     </row>
+    <row r="64" spans="1:12" ht="12.75">
+      <c r="A64" s="12">
+        <v>46234</v>
+      </c>
+      <c r="B64" s="13">
+        <v>1.1069999933242798</v>
+      </c>
+      <c r="C64" s="13">
+        <v>35.700000760000002</v>
+      </c>
+      <c r="D64" s="14">
+        <v>26.77592732691858</v>
+      </c>
+      <c r="E64" s="14">
+        <v>-35250.090060671617</v>
+      </c>
+      <c r="F64" s="15">
+        <v>-31842.899975831897</v>
+      </c>
+      <c r="G64" s="15">
+        <v>1316349.7340736755</v>
+      </c>
+      <c r="H64" s="15">
+        <v>1457199.1468319762</v>
+      </c>
+      <c r="I64" s="15">
+        <v>1158493.0294822238</v>
+      </c>
+      <c r="J64" s="15">
+        <v>1794259.6267486978</v>
+      </c>
+      <c r="K64" s="15">
+        <v>635766.59726647404</v>
+      </c>
+      <c r="L64" s="14">
+        <v>337060.4799167217</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -15899,7 +16072,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AM63"/>
+  <dimension ref="A1:AM64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -20061,6 +20234,71 @@
         <v>1.2</v>
       </c>
     </row>
+    <row r="64" spans="1:21" ht="12.75">
+      <c r="A64" s="12">
+        <v>46234</v>
+      </c>
+      <c r="B64" s="13">
+        <v>1.1069999933242798</v>
+      </c>
+      <c r="C64" s="13">
+        <v>35.700000760000002</v>
+      </c>
+      <c r="D64" s="14">
+        <v>26.77592732691858</v>
+      </c>
+      <c r="E64" s="14">
+        <v>-35250.090060671617</v>
+      </c>
+      <c r="F64" s="15">
+        <v>-31842.899975831897</v>
+      </c>
+      <c r="G64" s="15">
+        <v>1378502.5730276722</v>
+      </c>
+      <c r="H64" s="15">
+        <v>1526002.3391391358</v>
+      </c>
+      <c r="I64" s="15">
+        <v>1222236.9259249454</v>
+      </c>
+      <c r="J64" s="15">
+        <v>1904456.8522721031</v>
+      </c>
+      <c r="K64" s="15">
+        <v>682219.92634715769</v>
+      </c>
+      <c r="L64" s="14">
+        <v>378454.51313296735</v>
+      </c>
+      <c r="M64" s="23">
+        <v>1.281999945640564</v>
+      </c>
+      <c r="N64" s="23">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="O64" s="23">
+        <v>1.1546666622161865</v>
+      </c>
+      <c r="P64" s="23">
+        <v>1.0564761956532798</v>
+      </c>
+      <c r="Q64" s="23">
+        <v>9.8190466562906753E-2</v>
+      </c>
+      <c r="R64" s="23">
+        <v>8.5721089726402591E-2</v>
+      </c>
+      <c r="S64" s="9">
+        <v>1.2858163458960388E-3</v>
+      </c>
+      <c r="T64" s="9">
+        <v>76.364301073246494</v>
+      </c>
+      <c r="U64" s="11">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -20077,7 +20315,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AG63"/>
+  <dimension ref="A1:AG64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -23113,6 +23351,50 @@
         <v>1</v>
       </c>
     </row>
+    <row r="64" spans="1:14" ht="12.75">
+      <c r="A64" s="12">
+        <v>46234</v>
+      </c>
+      <c r="B64" s="13">
+        <v>1.1069999933242798</v>
+      </c>
+      <c r="C64" s="13">
+        <v>35.700000760000002</v>
+      </c>
+      <c r="D64" s="14">
+        <v>26.77592732691858</v>
+      </c>
+      <c r="E64" s="14">
+        <v>-35250.090060671617</v>
+      </c>
+      <c r="F64" s="15">
+        <v>-31842.899975831897</v>
+      </c>
+      <c r="G64" s="15">
+        <v>1399168.3450678764</v>
+      </c>
+      <c r="H64" s="15">
+        <v>1548879.3486496827</v>
+      </c>
+      <c r="I64" s="15">
+        <v>1226222.9374500697</v>
+      </c>
+      <c r="J64" s="15">
+        <v>1902459.1060100065</v>
+      </c>
+      <c r="K64" s="15">
+        <v>676236.16855993681</v>
+      </c>
+      <c r="L64" s="14">
+        <v>353579.75736032374</v>
+      </c>
+      <c r="M64" s="9">
+        <v>-82.62240642203966</v>
+      </c>
+      <c r="N64" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -23129,7 +23411,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG63"/>
+  <dimension ref="A1:AG64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -26165,6 +26447,50 @@
         <v>1</v>
       </c>
     </row>
+    <row r="64" spans="1:14" ht="12.75">
+      <c r="A64" s="12">
+        <v>46234</v>
+      </c>
+      <c r="B64" s="13">
+        <v>1.1069999933242798</v>
+      </c>
+      <c r="C64" s="13">
+        <v>35.700000760000002</v>
+      </c>
+      <c r="D64" s="14">
+        <v>26.77592732691858</v>
+      </c>
+      <c r="E64" s="14">
+        <v>-314574.39222416701</v>
+      </c>
+      <c r="F64" s="15">
+        <v>-284168.3777065904</v>
+      </c>
+      <c r="G64" s="15">
+        <v>11759663.097474437</v>
+      </c>
+      <c r="H64" s="15">
+        <v>13017946.970399981</v>
+      </c>
+      <c r="I64" s="15">
+        <v>9962785.3792499099</v>
+      </c>
+      <c r="J64" s="15">
+        <v>15927950.34825873</v>
+      </c>
+      <c r="K64" s="15">
+        <v>5965164.9690088201</v>
+      </c>
+      <c r="L64" s="14">
+        <v>2910003.3778587496</v>
+      </c>
+      <c r="M64" s="9">
+        <v>-82.62240642203966</v>
+      </c>
+      <c r="N64" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -26181,7 +26507,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AI63"/>
+  <dimension ref="A1:AI64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -29591,6 +29917,56 @@
         <v>1</v>
       </c>
     </row>
+    <row r="64" spans="1:16" ht="12.75">
+      <c r="A64" s="12">
+        <v>46234</v>
+      </c>
+      <c r="B64" s="13">
+        <v>1.1069999933242798</v>
+      </c>
+      <c r="C64" s="13">
+        <v>35.700000760000002</v>
+      </c>
+      <c r="D64" s="14">
+        <v>26.77592732691858</v>
+      </c>
+      <c r="E64" s="14">
+        <v>4485200</v>
+      </c>
+      <c r="F64" s="14">
+        <v>4013151.7473958335</v>
+      </c>
+      <c r="G64" s="14">
+        <v>-351576.30531150417</v>
+      </c>
+      <c r="H64" s="15">
+        <v>-317593.77365101298</v>
+      </c>
+      <c r="I64" s="15">
+        <v>11975755.658909511</v>
+      </c>
+      <c r="J64" s="15">
+        <v>13257161.434466034</v>
+      </c>
+      <c r="K64" s="15">
+        <v>8864712.2860347666</v>
+      </c>
+      <c r="L64" s="15">
+        <v>15310756.323999755</v>
+      </c>
+      <c r="M64" s="15">
+        <v>6446044.0379649885</v>
+      </c>
+      <c r="N64" s="14">
+        <v>2053594.8895337218</v>
+      </c>
+      <c r="O64" s="9">
+        <v>-82.62240642203966</v>
+      </c>
+      <c r="P64" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="J2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(CCI).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(CCI).xlsx
@@ -562,7 +562,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -748,6 +748,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -757,7 +760,7 @@
               <c:f>'model2(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -942,6 +945,9 @@
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>1158493.0294822238</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
               </c:numCache>
@@ -985,7 +991,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1171,6 +1177,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1180,7 +1189,7 @@
               <c:f>'model2(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1366,6 +1375,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1794259.6267486978</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1803474.034715408</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1408,7 +1420,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1594,6 +1606,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1603,7 +1618,7 @@
               <c:f>'model2(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1789,6 +1804,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>635766.59726647404</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>644981.0052331842</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1810,11 +1828,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="541882624"/>
-        <c:axId val="542040064"/>
+        <c:axId val="413639808"/>
+        <c:axId val="427077632"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="541882624"/>
+        <c:axId val="413639808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1857,14 +1875,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="542040064"/>
+        <c:crossAx val="427077632"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="542040064"/>
+        <c:axId val="427077632"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1915,7 +1933,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="541882624"/>
+        <c:crossAx val="413639808"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2076,7 +2094,7 @@
               <c:f>'model2(2)vol&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2262,6 +2280,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-351576.30531150417</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-130359.36832865544</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2276,8 +2297,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="567400704"/>
-        <c:axId val="567399168"/>
+        <c:axId val="444635392"/>
+        <c:axId val="444633856"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2302,7 +2323,7 @@
               <c:f>'model2(2)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2488,6 +2509,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2497,7 +2521,7 @@
               <c:f>'model2(2)vol&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2683,6 +2707,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2699,11 +2726,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="567395840"/>
-        <c:axId val="567397376"/>
+        <c:axId val="444626432"/>
+        <c:axId val="444627968"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="567395840"/>
+        <c:axId val="444626432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2746,14 +2773,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="567397376"/>
+        <c:crossAx val="444627968"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="567397376"/>
+        <c:axId val="444627968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2804,12 +2831,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="567395840"/>
+        <c:crossAx val="444626432"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="567399168"/>
+        <c:axId val="444633856"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2846,12 +2873,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="567400704"/>
+        <c:crossAx val="444635392"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="567400704"/>
+        <c:axId val="444635392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2860,7 +2887,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="567399168"/>
+        <c:crossAx val="444633856"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2992,7 +3019,7 @@
               <c:f>'model2(1)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3178,6 +3205,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-35250.090060671617</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-34946.17272282279</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3192,8 +3222,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="676456320"/>
-        <c:axId val="676454400"/>
+        <c:axId val="444758656"/>
+        <c:axId val="444756736"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -3218,7 +3248,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3404,6 +3434,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3413,7 +3446,7 @@
               <c:f>'model2(1)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -3599,6 +3632,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3615,11 +3651,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="572617088"/>
-        <c:axId val="572619008"/>
+        <c:axId val="430380160"/>
+        <c:axId val="430382080"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="572617088"/>
+        <c:axId val="430380160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3662,14 +3698,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="572619008"/>
+        <c:crossAx val="430382080"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="572619008"/>
+        <c:axId val="430382080"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3720,12 +3756,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="572617088"/>
+        <c:crossAx val="430380160"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="676454400"/>
+        <c:axId val="444756736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3762,12 +3798,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="676456320"/>
+        <c:crossAx val="444758656"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="676456320"/>
+        <c:axId val="444758656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3776,7 +3812,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="676454400"/>
+        <c:crossAx val="444756736"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3926,7 +3962,7 @@
               <c:f>'model2(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4112,6 +4148,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4121,7 +4160,7 @@
               <c:f>'model2(1)&amp;CCI_per_month'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4306,6 +4345,9 @@
                   <c:v>1222236.9259249454</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>1222236.9259249454</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>1222236.9259249454</c:v>
                 </c:pt>
               </c:numCache>
@@ -4349,7 +4391,7 @@
               <c:f>'model2(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4535,6 +4577,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4544,7 +4589,7 @@
               <c:f>'model2(1)&amp;CCI_per_month'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4730,6 +4775,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1904456.8522721031</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1914106.3282147367</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4772,7 +4820,7 @@
               <c:f>'model2(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4958,6 +5006,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4967,7 +5018,7 @@
               <c:f>'model2(1)&amp;CCI_per_month'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5153,6 +5204,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>682219.92634715769</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>691869.40228979127</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5174,11 +5228,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="677705600"/>
-        <c:axId val="677724160"/>
+        <c:axId val="488275328"/>
+        <c:axId val="488740352"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="677705600"/>
+        <c:axId val="488275328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5221,14 +5275,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="677724160"/>
+        <c:crossAx val="488740352"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="677724160"/>
+        <c:axId val="488740352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5279,7 +5333,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="677705600"/>
+        <c:crossAx val="488275328"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5440,7 +5494,7 @@
               <c:f>'model2(1)&amp;CCI_per_month'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5626,6 +5680,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-35250.090060671617</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-34946.17272282279</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5640,8 +5697,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="412220800"/>
-        <c:axId val="412219264"/>
+        <c:axId val="429120896"/>
+        <c:axId val="429119360"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -5666,7 +5723,7 @@
               <c:f>'model2(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5852,6 +5909,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5861,7 +5921,7 @@
               <c:f>'model2(1)&amp;CCI_per_month'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -6047,6 +6107,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6063,11 +6126,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="412211840"/>
-        <c:axId val="412217728"/>
+        <c:axId val="526649600"/>
+        <c:axId val="429117824"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="412211840"/>
+        <c:axId val="526649600"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6110,14 +6173,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="412217728"/>
+        <c:crossAx val="429117824"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="412217728"/>
+        <c:axId val="429117824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6168,12 +6231,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="412211840"/>
+        <c:crossAx val="526649600"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="412219264"/>
+        <c:axId val="429119360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6210,12 +6273,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="412220800"/>
+        <c:crossAx val="429120896"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="412220800"/>
+        <c:axId val="429120896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6224,7 +6287,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="412219264"/>
+        <c:crossAx val="429119360"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6374,7 +6437,7 @@
               <c:f>'model2(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6560,6 +6623,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6569,7 +6635,7 @@
               <c:f>'model2(1)&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6754,6 +6820,9 @@
                   <c:v>1226222.9374500697</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>1226222.9374500697</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>1226222.9374500697</c:v>
                 </c:pt>
               </c:numCache>
@@ -6797,7 +6866,7 @@
               <c:f>'model2(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6983,6 +7052,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6992,7 +7064,7 @@
               <c:f>'model2(1)&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7178,6 +7250,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1902459.1060100065</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1912253.2417262525</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7220,7 +7295,7 @@
               <c:f>'model2(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7406,6 +7481,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7415,7 +7493,7 @@
               <c:f>'model2(1)&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7601,6 +7679,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>676236.16855993681</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>686030.30427618278</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7622,11 +7703,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="566295168"/>
-        <c:axId val="566296960"/>
+        <c:axId val="430439040"/>
+        <c:axId val="430444928"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="566295168"/>
+        <c:axId val="430439040"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7669,14 +7750,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566296960"/>
+        <c:crossAx val="430444928"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="566296960"/>
+        <c:axId val="430444928"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7727,7 +7808,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566295168"/>
+        <c:crossAx val="430439040"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7888,7 +7969,7 @@
               <c:f>'model2(1)&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8074,6 +8155,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-35250.090060671617</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-34946.17272282279</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8088,8 +8172,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="566340992"/>
-        <c:axId val="566339456"/>
+        <c:axId val="430476672"/>
+        <c:axId val="430475136"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -8114,7 +8198,7 @@
               <c:f>'model2(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8300,6 +8384,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8309,7 +8396,7 @@
               <c:f>'model2(1)&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8495,6 +8582,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8511,11 +8601,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="566319744"/>
-        <c:axId val="566337920"/>
+        <c:axId val="430463616"/>
+        <c:axId val="430473600"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="566319744"/>
+        <c:axId val="430463616"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8558,14 +8648,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566337920"/>
+        <c:crossAx val="430473600"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="566337920"/>
+        <c:axId val="430473600"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8616,12 +8706,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566319744"/>
+        <c:crossAx val="430463616"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="566339456"/>
+        <c:axId val="430475136"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8658,12 +8748,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566340992"/>
+        <c:crossAx val="430476672"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="566340992"/>
+        <c:axId val="430476672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8672,7 +8762,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="566339456"/>
+        <c:crossAx val="430475136"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8822,7 +8912,7 @@
               <c:f>'model2(2)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9008,6 +9098,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9017,7 +9110,7 @@
               <c:f>'model2(2)&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9202,6 +9295,9 @@
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>9962785.3792499099</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
               </c:numCache>
@@ -9245,7 +9341,7 @@
               <c:f>'model2(2)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9431,6 +9527,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9440,7 +9539,7 @@
               <c:f>'model2(2)&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9626,6 +9725,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>15927950.34825873</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>16010267.631064614</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9668,7 +9770,7 @@
               <c:f>'model2(2)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9854,6 +9956,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9863,7 +9968,7 @@
               <c:f>'model2(2)&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10049,6 +10154,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>5965164.9690088201</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>6047482.2518147044</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10070,11 +10178,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="566381184"/>
-        <c:axId val="566399360"/>
+        <c:axId val="444353152"/>
+        <c:axId val="444363136"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="566381184"/>
+        <c:axId val="444353152"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10117,14 +10225,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566399360"/>
+        <c:crossAx val="444363136"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="566399360"/>
+        <c:axId val="444363136"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10175,7 +10283,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566381184"/>
+        <c:crossAx val="444353152"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10336,7 +10444,7 @@
               <c:f>'model2(2)&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10522,6 +10630,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>11759663.097474437</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>11482128.604656462</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10536,8 +10647,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="566430720"/>
-        <c:axId val="566429184"/>
+        <c:axId val="444386304"/>
+        <c:axId val="444384768"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10562,7 +10673,7 @@
               <c:f>'model2(2)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10748,6 +10859,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10757,7 +10871,7 @@
               <c:f>'model2(2)&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10943,6 +11057,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10959,11 +11076,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="566417664"/>
-        <c:axId val="566427648"/>
+        <c:axId val="444381440"/>
+        <c:axId val="444383232"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="566417664"/>
+        <c:axId val="444381440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11006,14 +11123,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566427648"/>
+        <c:crossAx val="444383232"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="566427648"/>
+        <c:axId val="444383232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11064,12 +11181,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566417664"/>
+        <c:crossAx val="444381440"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="566429184"/>
+        <c:axId val="444384768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11106,12 +11223,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566430720"/>
+        <c:crossAx val="444386304"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="566430720"/>
+        <c:axId val="444386304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11120,7 +11237,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="566429184"/>
+        <c:crossAx val="444384768"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11270,7 +11387,7 @@
               <c:f>'model2(2)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11456,6 +11573,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11465,7 +11585,7 @@
               <c:f>'model2(2)vol&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11650,6 +11770,9 @@
                   <c:v>8864712.2860347666</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>8864712.2860347666</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>8864712.2860347666</c:v>
                 </c:pt>
               </c:numCache>
@@ -11693,7 +11816,7 @@
               <c:f>'model2(2)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11879,6 +12002,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11888,7 +12014,7 @@
               <c:f>'model2(2)vol&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12074,6 +12200,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>15310756.323999755</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>15394586.248141063</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12116,7 +12245,7 @@
               <c:f>'model2(2)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12302,6 +12431,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12311,7 +12443,7 @@
               <c:f>'model2(2)vol&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12497,6 +12629,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>6446044.0379649885</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>6529873.9621062968</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12518,11 +12653,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="567372032"/>
-        <c:axId val="567373824"/>
+        <c:axId val="444610432"/>
+        <c:axId val="444611968"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="567372032"/>
+        <c:axId val="444610432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12565,14 +12700,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="567373824"/>
+        <c:crossAx val="444611968"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="567373824"/>
+        <c:axId val="444611968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12623,7 +12758,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="567372032"/>
+        <c:crossAx val="444610432"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13337,7 +13472,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG64"/>
+  <dimension ref="A1:AG65"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -16056,6 +16191,44 @@
         <v>337060.4799167217</v>
       </c>
     </row>
+    <row r="65" spans="1:12" ht="12.75">
+      <c r="A65" s="12">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="13">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="13">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="14">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="14">
+        <v>-34946.17272282279</v>
+      </c>
+      <c r="F65" s="15">
+        <v>-31369.994514880033</v>
+      </c>
+      <c r="G65" s="15">
+        <v>1284979.7395587955</v>
+      </c>
+      <c r="H65" s="15">
+        <v>1431467.3820758634</v>
+      </c>
+      <c r="I65" s="15">
+        <v>1158493.0294822238</v>
+      </c>
+      <c r="J65" s="15">
+        <v>1803474.034715408</v>
+      </c>
+      <c r="K65" s="15">
+        <v>644981.0052331842</v>
+      </c>
+      <c r="L65" s="14">
+        <v>372006.65263954451</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -16072,7 +16245,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AM64"/>
+  <dimension ref="A1:AM65"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -20299,6 +20472,71 @@
         <v>1</v>
       </c>
     </row>
+    <row r="65" spans="1:21" ht="12.75">
+      <c r="A65" s="12">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="13">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="13">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="14">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="14">
+        <v>-34946.17272282279</v>
+      </c>
+      <c r="F65" s="15">
+        <v>-31369.994514880033</v>
+      </c>
+      <c r="G65" s="15">
+        <v>1347132.5785127922</v>
+      </c>
+      <c r="H65" s="15">
+        <v>1500705.6423589466</v>
+      </c>
+      <c r="I65" s="15">
+        <v>1222236.9259249454</v>
+      </c>
+      <c r="J65" s="15">
+        <v>1914106.3282147367</v>
+      </c>
+      <c r="K65" s="15">
+        <v>691869.40228979127</v>
+      </c>
+      <c r="L65" s="14">
+        <v>413400.68585579016</v>
+      </c>
+      <c r="M65" s="23">
+        <v>1.1759999990463257</v>
+      </c>
+      <c r="N65" s="23">
+        <v>1.093000054359436</v>
+      </c>
+      <c r="O65" s="23">
+        <v>1.1276666720708211</v>
+      </c>
+      <c r="P65" s="23">
+        <v>1.0799047677289875</v>
+      </c>
+      <c r="Q65" s="23">
+        <v>4.7761904341833583E-2</v>
+      </c>
+      <c r="R65" s="23">
+        <v>7.0020411087542242E-2</v>
+      </c>
+      <c r="S65" s="9">
+        <v>1.0503061663131336E-3</v>
+      </c>
+      <c r="T65" s="9">
+        <v>45.47426824074654</v>
+      </c>
+      <c r="U65" s="11">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -20315,7 +20553,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AG64"/>
+  <dimension ref="A1:AG65"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -23395,6 +23633,50 @@
         <v>1</v>
       </c>
     </row>
+    <row r="65" spans="1:14" ht="12.75">
+      <c r="A65" s="12">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="13">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="13">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="14">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="14">
+        <v>-34946.17272282279</v>
+      </c>
+      <c r="F65" s="15">
+        <v>-31369.994514880033</v>
+      </c>
+      <c r="G65" s="15">
+        <v>1367798.3505529964</v>
+      </c>
+      <c r="H65" s="15">
+        <v>1523727.3116431059</v>
+      </c>
+      <c r="I65" s="15">
+        <v>1226222.9374500697</v>
+      </c>
+      <c r="J65" s="15">
+        <v>1912253.2417262525</v>
+      </c>
+      <c r="K65" s="15">
+        <v>686030.30427618278</v>
+      </c>
+      <c r="L65" s="14">
+        <v>388525.93008314655</v>
+      </c>
+      <c r="M65" s="9">
+        <v>-90.561561933820059</v>
+      </c>
+      <c r="N65" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -23411,7 +23693,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG64"/>
+  <dimension ref="A1:AG65"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -26491,6 +26773,50 @@
         <v>1</v>
       </c>
     </row>
+    <row r="65" spans="1:14" ht="12.75">
+      <c r="A65" s="12">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="13">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="13">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="14">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="14">
+        <v>-309173.41467680095</v>
+      </c>
+      <c r="F65" s="15">
+        <v>-277534.492817975</v>
+      </c>
+      <c r="G65" s="15">
+        <v>11482128.604656462</v>
+      </c>
+      <c r="H65" s="15">
+        <v>12791090.838529063</v>
+      </c>
+      <c r="I65" s="15">
+        <v>9962785.3792499099</v>
+      </c>
+      <c r="J65" s="15">
+        <v>16010267.631064614</v>
+      </c>
+      <c r="K65" s="15">
+        <v>6047482.2518147044</v>
+      </c>
+      <c r="L65" s="14">
+        <v>3219176.7925355504</v>
+      </c>
+      <c r="M65" s="9">
+        <v>-90.561561933820059</v>
+      </c>
+      <c r="N65" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -26507,7 +26833,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AI64"/>
+  <dimension ref="A1:AI65"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -29967,6 +30293,56 @@
         <v>1</v>
       </c>
     </row>
+    <row r="65" spans="1:16" ht="12.75">
+      <c r="A65" s="12">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="13">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="13">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="14">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="14">
+        <v>1687200</v>
+      </c>
+      <c r="F65" s="14">
+        <v>4001533.5447742641</v>
+      </c>
+      <c r="G65" s="14">
+        <v>-130359.36832865544</v>
+      </c>
+      <c r="H65" s="15">
+        <v>-117019.18553050711</v>
+      </c>
+      <c r="I65" s="15">
+        <v>11858736.473379003</v>
+      </c>
+      <c r="J65" s="15">
+        <v>13210631.990278685</v>
+      </c>
+      <c r="K65" s="15">
+        <v>8864712.2860347666</v>
+      </c>
+      <c r="L65" s="15">
+        <v>15394586.248141063</v>
+      </c>
+      <c r="M65" s="15">
+        <v>6529873.9621062968</v>
+      </c>
+      <c r="N65" s="14">
+        <v>2183954.2578623774</v>
+      </c>
+      <c r="O65" s="9">
+        <v>-90.561561933820059</v>
+      </c>
+      <c r="P65" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="J2">
